--- a/Sources/المستهدف.xlsx
+++ b/Sources/المستهدف.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Desktop\NDEDC_Production\Sources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7aa1d8f405ba1d72/NDEDC_Production/Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69269F31-B93F-4A4D-ADD3-A805192EAECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{69269F31-B93F-4A4D-ADD3-A805192EAECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6434ABCD-C420-4876-BE0A-271DC2C7D2E0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>القطاعات</t>
   </si>
   <si>
-    <t>A4-A5</t>
-  </si>
-  <si>
     <t>A3</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>الأجمالي</t>
+  </si>
+  <si>
+    <t>A4+A5</t>
   </si>
 </sst>
 </file>
@@ -239,7 +239,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -275,7 +275,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -370,32 +370,6 @@
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -422,37 +396,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -504,14 +447,57 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -519,18 +505,9 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -564,7 +541,30 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -593,11 +593,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2839315E-6770-4451-9533-495B6E1685CE}" name="Table13" displayName="Table13" ref="A1:B60" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2839315E-6770-4451-9533-495B6E1685CE}" name="Table13" displayName="Table13" ref="A1:B60" totalsRowCount="1" headerRowDxfId="9" dataDxfId="7" totalsRowDxfId="5" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:B59" xr:uid="{2839315E-6770-4451-9533-495B6E1685CE}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{05FE433A-4BB6-4577-97BE-C875A73AD801}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{60CAE18C-23CF-4716-A464-02978E7BE3E4}" name="A4-A5" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="1" xr3:uid="{05FE433A-4BB6-4577-97BE-C875A73AD801}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="3" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{60CAE18C-23CF-4716-A464-02978E7BE3E4}" name="A4+A5" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="0">
       <totalsRowFormula>SUBTOTAL(109,B43:B59)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -869,33 +869,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="5" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B2" s="3">
         <v>193</v>
@@ -910,9 +910,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
         <v>324</v>
@@ -927,9 +927,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3">
         <v>271</v>
@@ -944,9 +944,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
         <v>240</v>
@@ -961,9 +961,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
         <v>421</v>
@@ -978,9 +978,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
         <v>223</v>
@@ -995,9 +995,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3">
         <v>364</v>
@@ -1012,9 +1012,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3">
         <v>254</v>
@@ -1029,9 +1029,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
         <v>308</v>
@@ -1046,9 +1046,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>230</v>
@@ -1063,9 +1063,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3">
         <v>260</v>
@@ -1080,9 +1080,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3">
         <v>296</v>
@@ -1097,9 +1097,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
         <v>119</v>
@@ -1114,9 +1114,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3">
         <v>297</v>
@@ -1131,9 +1131,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="6">
         <f>SUBTOTAL(109,B2:B15)</f>
@@ -1152,9 +1152,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3">
         <v>310</v>
@@ -1169,9 +1169,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>535</v>
@@ -1186,9 +1186,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3">
         <v>250</v>
@@ -1203,9 +1203,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="3">
         <v>95</v>
@@ -1220,9 +1220,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="3">
         <v>829</v>
@@ -1237,9 +1237,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="3">
         <v>232</v>
@@ -1254,9 +1254,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3">
         <v>162</v>
@@ -1271,9 +1271,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="3">
         <v>434</v>
@@ -1288,9 +1288,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="3">
         <v>369</v>
@@ -1305,9 +1305,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3">
         <v>281</v>
@@ -1322,9 +1322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="3">
         <v>299</v>
@@ -1339,9 +1339,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="6">
         <f>SUBTOTAL(109,B17:B27)</f>
@@ -1360,9 +1360,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="3">
         <v>707</v>
@@ -1377,9 +1377,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="3">
         <v>880</v>
@@ -1394,9 +1394,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="3">
         <v>637</v>
@@ -1411,9 +1411,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="3">
         <v>371</v>
@@ -1428,9 +1428,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="3">
         <v>497</v>
@@ -1445,9 +1445,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3">
         <v>387</v>
@@ -1462,9 +1462,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="3">
         <v>760</v>
@@ -1479,9 +1479,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3">
         <v>139</v>
@@ -1496,9 +1496,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3">
         <v>571</v>
@@ -1513,9 +1513,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3">
         <v>275</v>
@@ -1530,9 +1530,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3">
         <v>339</v>
@@ -1547,9 +1547,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="3">
         <v>475</v>
@@ -1564,9 +1564,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3">
         <v>345</v>
@@ -1581,9 +1581,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6">
         <f>SUBTOTAL(109,B29:B41)</f>
@@ -1602,9 +1602,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="3">
         <v>446</v>
@@ -1619,9 +1619,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="3">
         <v>357</v>
@@ -1636,9 +1636,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3">
         <v>332</v>
@@ -1653,9 +1653,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="3">
         <v>313</v>
@@ -1670,9 +1670,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="3">
         <v>389</v>
@@ -1687,9 +1687,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="3">
         <v>353</v>
@@ -1704,9 +1704,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="3">
         <v>435</v>
@@ -1721,9 +1721,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3">
         <v>201</v>
@@ -1738,9 +1738,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="3">
         <v>385</v>
@@ -1755,9 +1755,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="3">
         <v>225</v>
@@ -1772,9 +1772,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="3">
         <v>332</v>
@@ -1789,9 +1789,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="3">
         <v>586</v>
@@ -1806,9 +1806,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="3">
         <v>243</v>
@@ -1823,9 +1823,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3">
         <v>333</v>
@@ -1840,9 +1840,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" s="3">
         <v>502</v>
@@ -1857,9 +1857,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="3">
         <v>365</v>
@@ -1874,9 +1874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="3">
         <v>155</v>
@@ -1891,9 +1891,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="6">
         <f>SUBTOTAL(109,B43:B59)</f>
@@ -1912,24 +1912,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="8">
-        <f>B16+B28+B42+Table13[[#Totals],[A4-A5]]</f>
+        <f>B16+B28+B42+Table13[[#Totals],[A4+A5]]</f>
         <v>19931</v>
       </c>
       <c r="C61" s="8">
-        <f>C16+C28+C42+Table13[[#Totals],[A4-A5]]</f>
+        <f>C16+C28+C42+Table13[[#Totals],[A4+A5]]</f>
         <v>5952</v>
       </c>
       <c r="D61" s="8">
-        <f>D16+D28+D42+Table13[[#Totals],[A4-A5]]</f>
+        <f>D16+D28+D42+Table13[[#Totals],[A4+A5]]</f>
         <v>5952</v>
       </c>
       <c r="E61" s="8">
-        <f>E16+E28+E42+Table13[[#Totals],[A4-A5]]</f>
+        <f>E16+E28+E42+Table13[[#Totals],[A4+A5]]</f>
         <v>5952</v>
       </c>
     </row>
